--- a/data/confidence-intervals-for-proportions-and-differences--ab_test.xlsx
+++ b/data/confidence-intervals-for-proportions-and-differences--ab_test.xlsx
@@ -60530,7 +60530,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vxxxxx</t>
+          <t>Vxxxxxx</t>
         </is>
       </c>
     </row>
@@ -60671,7 +60671,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: a randomized A/B test log, one row per visitor.</t>
+          <t>WHAT IS CAPTURED: a randomized A/B test log, one row per visitor (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
